--- a/ig/DM-DECEMBRE-2025/CodeSystem-TRE-R344-NiveauExpertise.xlsx
+++ b/ig/DM-DECEMBRE-2025/CodeSystem-TRE-R344-NiveauExpertise.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="137">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250623120000</t>
+    <t>20251222120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-23T12:00:00+01:00</t>
+    <t>2025-12-22T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,219 +118,222 @@
     <t>Count</t>
   </si>
   <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Uri</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>dateValid</t>
+  </si>
+  <si>
+    <t>date de validité d'un code concept</t>
+  </si>
+  <si>
+    <t>dateTime</t>
+  </si>
+  <si>
+    <t>dateMaj</t>
+  </si>
+  <si>
+    <t>Date de mise à jour d'un code concept</t>
+  </si>
+  <si>
+    <t>dateFin</t>
+  </si>
+  <si>
+    <t>Date de fin d'exploitation d'un code concept</t>
+  </si>
+  <si>
+    <t>deprecationDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
+  </si>
+  <si>
+    <t>Date Concept was deprecated</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#status</t>
+  </si>
+  <si>
+    <t>A property that indicates the status of the concept.</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>retirementDate</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
+  </si>
+  <si>
+    <t>Date Concept was retired</t>
+  </si>
+  <si>
+    <t>Level</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>Definition</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Centre de référence labellisé</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Centre de compétences labellisé</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Structure spécialisée labellisée</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des personnes en état de conscience altérée</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des patients amputés, appareillés ou non</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation neuro-orthopédique</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation post-réanimation (SRPR)</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des troubles des patients cérébro-lésés</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des lésions médullaires</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des obésités complexes</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation troubles cognitifs liés à une conduite addictive</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation du polyhandicap</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>SMR Labellisé réadaptation des troubles du langage et des apprentissages</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>Centre de recours pour chirurgie oncologique complexe</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>Premier niveau de recours</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>Deuxième niveau de recours</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>Troisième niveau de recours</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>Unité de réanimation pédiatrique de recours</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>Filière endométriose - premier niveau de recours</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>Filière endométriose - deuxième niveau de recours</t>
+  </si>
+  <si>
     <t>33</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Uri</t>
-  </si>
-  <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>dateValid</t>
-  </si>
-  <si>
-    <t>date de validité d'un code concept</t>
-  </si>
-  <si>
-    <t>dateTime</t>
-  </si>
-  <si>
-    <t>dateMaj</t>
-  </si>
-  <si>
-    <t>Date de mise à jour d'un code concept</t>
-  </si>
-  <si>
-    <t>dateFin</t>
-  </si>
-  <si>
-    <t>Date de fin d'exploitation d'un code concept</t>
-  </si>
-  <si>
-    <t>deprecationDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#deprecationDate</t>
-  </si>
-  <si>
-    <t>Date Concept was deprecated</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#status</t>
-  </si>
-  <si>
-    <t>A property that indicates the status of the concept.</t>
-  </si>
-  <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>retirementDate</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/concept-properties#retirementDate</t>
-  </si>
-  <si>
-    <t>Date Concept was retired</t>
-  </si>
-  <si>
-    <t>Level</t>
-  </si>
-  <si>
-    <t>Display</t>
-  </si>
-  <si>
-    <t>Definition</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>Centre de référence labellisé</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>Centre de compétences labellisé</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>Structure spécialisée labellisée</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des personnes en état de conscience altérée</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des patients amputés, appareillés ou non</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Cardiologique (PREPAC)</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Respiratoire (PREPAR)</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation neuro-orthopédique</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation post-réanimation (SRPR)</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation PREcoce Post-Aiguë Neurologique (PREPAN)</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des troubles des patients cérébro-lésés</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des lésions médullaires</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des obésités complexes</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation troubles cognitifs liés à une conduite addictive</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation du polyhandicap</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>SMR Labellisé réadaptation des troubles du langage et des apprentissages</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>Centre de recours pour chirurgie oncologique complexe</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>Premier niveau de recours</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>Deuxième niveau de recours</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>Troisième niveau de recours</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>Unité de réanimation pédiatrique de recours</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>Filière endométriose - premier niveau de recours</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>Filière endométriose - deuxième niveau de recours</t>
-  </si>
-  <si>
     <t>Filière endométriose - troisième niveau de recours</t>
   </si>
   <si>
@@ -364,9 +367,6 @@
     <t>Unité neuro-vasculaire (UNV) de recours</t>
   </si>
   <si>
-    <t>39</t>
-  </si>
-  <si>
     <t>Filière Obésité - Niveau 1 Conventionné Centres Spécialisés Obésité (CSO)</t>
   </si>
   <si>
@@ -389,6 +389,42 @@
   </si>
   <si>
     <t>Filière Obésité - Niveau 3 (Centre Spécialisé Obésité)</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>Centre Ressources Autisme (CRA)</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>Centre de référence des Troubles du Langage et de l’Apprentissage (CRTLA)</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>Centre de référence du Trouble Déficit de l’Attention avec ou sans Hyperactivité (CRTDAH)</t>
+  </si>
+  <si>
+    <t>46</t>
+  </si>
+  <si>
+    <t>Centre de compétence centre mémoire ressources et recherche (CMRR)</t>
+  </si>
+  <si>
+    <t>47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Centre expert Parkinson </t>
+  </si>
+  <si>
+    <t>48</t>
+  </si>
+  <si>
+    <t>Centre de ressources et de compétences sclérose en plaques (SEP)</t>
   </si>
 </sst>
 </file>
@@ -798,7 +834,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1096,10 +1132,10 @@
         <v>58</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>34</v>
+        <v>105</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D25" s="2"/>
     </row>
@@ -1108,10 +1144,10 @@
         <v>58</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D26" s="2"/>
     </row>
@@ -1120,10 +1156,10 @@
         <v>58</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D27" s="2"/>
     </row>
@@ -1132,10 +1168,10 @@
         <v>58</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D28" s="2"/>
     </row>
@@ -1144,10 +1180,10 @@
         <v>58</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D29" s="2"/>
     </row>
@@ -1156,10 +1192,10 @@
         <v>58</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D30" s="2"/>
     </row>
@@ -1168,7 +1204,7 @@
         <v>58</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>116</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s" s="2">
         <v>117</v>
@@ -1212,6 +1248,78 @@
         <v>124</v>
       </c>
       <c r="D34" s="2"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="C35" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C37" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="2">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>135</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="D40" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
